--- a/patch-uml/ig/StructureDefinition-tddui-patient.xlsx
+++ b/patch-uml/ig/StructureDefinition-tddui-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:06:06+00:00</t>
+    <t>2026-06-16T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
